--- a/data/trans_orig/P33_MIN_2023_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33_MIN_2023_R-Clase-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nº medio de minutos durante los cuales la población se echa la siesta</t>
+          <t>Nº medio de minutos durante los cuales la población se echa la siesta (tasa de respuesta: 37,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,09; 37,67</t>
+          <t>26,26; 37,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,04; 29,22</t>
+          <t>19,98; 29,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,17; 33,44</t>
+          <t>25,23; 33,23</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,7; 39,43</t>
+          <t>28,17; 39,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,2; 34,83</t>
+          <t>23,39; 34,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,93; 36,18</t>
+          <t>27,62; 35,81</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 41,63</t>
+          <t>3,95; 40,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,54; 37,65</t>
+          <t>23,65; 37,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 38,62</t>
+          <t>4,93; 39,14</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,97; 46,22</t>
+          <t>37,87; 45,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 40,25</t>
+          <t>6,09; 40,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,35; 41,84</t>
+          <t>15,37; 41,76</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,9; 50,19</t>
+          <t>36,95; 49,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,65; 40,36</t>
+          <t>32,66; 40,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,9; 42,73</t>
+          <t>35,98; 42,73</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,42; 42,07</t>
+          <t>8,52; 39,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41,54; 55,7</t>
+          <t>40,83; 55,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38,46; 52,53</t>
+          <t>39,32; 52,47</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,17; 38,7</t>
+          <t>18,99; 38,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,91; 37,81</t>
+          <t>16,95; 37,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,38; 37,69</t>
+          <t>22,14; 37,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33_MIN_2023_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33_MIN_2023_R-Clase-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>31,38</t>
+          <t>31,13</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24,73</t>
+          <t>25,66</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28,86</t>
+          <t>29,05</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,26; 37,77</t>
+          <t>26,5; 37,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,98; 29,32</t>
+          <t>21,39; 30,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,23; 33,23</t>
+          <t>25,34; 32,92</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>33,37</t>
+          <t>33,68</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28,74</t>
+          <t>28,65</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31,64</t>
+          <t>31,77</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,17; 39,61</t>
+          <t>28,07; 39,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,39; 34,4</t>
+          <t>23,87; 35,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,62; 35,81</t>
+          <t>28,17; 36,35</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>16,28</t>
+          <t>38,66</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>30,11</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17,77</t>
+          <t>36,76</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,95; 40,92</t>
+          <t>32,27; 48,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,65; 37,22</t>
+          <t>23,59; 37,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,93; 39,14</t>
+          <t>31,57; 43,52</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>41,74</t>
+          <t>41,82</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20,24</t>
+          <t>39,11</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>40,9</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,87; 45,77</t>
+          <t>37,97; 45,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 40,6</t>
+          <t>34,11; 44,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,37; 41,76</t>
+          <t>37,98; 44,03</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>42,69</t>
+          <t>42,54</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>36,37</t>
+          <t>36,54</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39,09</t>
+          <t>39,11</t>
         </is>
       </c>
     </row>
@@ -771,24 +771,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,95; 49,48</t>
+          <t>37,1; 49,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,66; 40,43</t>
+          <t>33,13; 40,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,98; 42,73</t>
+          <t>35,82; 42,23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -798,17 +798,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>21,98</t>
+          <t>29,97</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>46,88</t>
+          <t>46,96</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44,44</t>
+          <t>45,51</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,52; 39,23</t>
+          <t>12,92; 52,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40,83; 55,8</t>
+          <t>41,15; 55,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39,32; 52,47</t>
+          <t>39,85; 53,06</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>31,78</t>
+          <t>38,22</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>31,26</t>
+          <t>37,41</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31,54</t>
+          <t>37,85</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,99; 38,57</t>
+          <t>35,97; 40,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,95; 37,99</t>
+          <t>35,09; 40,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22,14; 37,29</t>
+          <t>36,36; 39,78</t>
         </is>
       </c>
     </row>
